--- a/data/Terre di Pedemonte/investment_decision/municipality_level_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/municipality_level_investment_decision.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -499,26 +499,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.0867453946648023</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -536,26 +536,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.1343372936492743</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -573,26 +573,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.1647522628953677</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -610,26 +610,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.1862401701876625</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -647,26 +647,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.202571092960545</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_HotWaterTank_s_175 MWh</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_HotWaterTank_s_175 MWh</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_HotWaterTank_s_175 MWh</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_HotWaterTank_s_175 MWh</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_HotWaterTank_s_175 MWh</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>9.670513822735714</v>
       </c>
     </row>
     <row r="12">
@@ -869,32 +869,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>0.3488360334833763</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>0.3488360334833763</v>
       </c>
     </row>
     <row r="13">
@@ -906,32 +906,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>100</v>
+        <v>0.5504795012061273</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>0.5504795012061273</v>
       </c>
     </row>
     <row r="14">
@@ -939,36 +939,36 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>100</v>
+        <v>0.6851905894951467</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>0.6851905894951467</v>
       </c>
     </row>
     <row r="15">
@@ -976,36 +976,36 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>100</v>
+        <v>0.7842950655215264</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>0.7842950655215264</v>
       </c>
     </row>
     <row r="16">
@@ -1013,36 +1013,36 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>4.355717577953295</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>100</v>
+        <v>0.8622572055472979</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>0.8622572055472979</v>
       </c>
     </row>
     <row r="17">
@@ -1050,36 +1050,36 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>1.116330273373379</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>4.15</v>
       </c>
       <c r="E17" t="n">
-        <v>22.75</v>
+        <v>3.148711502134913</v>
       </c>
       <c r="F17" t="n">
-        <v>1.116330273373552</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>8.25</v>
+        <v>3.148711502134913</v>
       </c>
       <c r="H17" t="n">
-        <v>1.116330273373508</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>22.75</v>
+        <v>0.2521706266144889</v>
       </c>
       <c r="J17" t="n">
-        <v>1.116330273373552</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>8.25</v>
+        <v>0.2521706266144889</v>
       </c>
     </row>
     <row r="18">
@@ -1087,36 +1087,36 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>17.92678992003999</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4.15</v>
       </c>
       <c r="E18" t="n">
-        <v>22.75</v>
+        <v>3.148711502134913</v>
       </c>
       <c r="F18" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>8.25</v>
+        <v>3.148711502134913</v>
       </c>
       <c r="H18" t="n">
-        <v>17.9530724770768</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>22.75</v>
+        <v>0.3979369888237065</v>
       </c>
       <c r="J18" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>8.25</v>
+        <v>0.3979369888237065</v>
       </c>
     </row>
     <row r="19">
@@ -1124,36 +1124,36 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>21.15337934071444</v>
+        <v>0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4.15</v>
       </c>
       <c r="E19" t="n">
-        <v>22.75</v>
+        <v>3.148711502134913</v>
       </c>
       <c r="F19" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>8.25</v>
+        <v>3.148711502134913</v>
       </c>
       <c r="H19" t="n">
-        <v>21.20860741999773</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>22.75</v>
+        <v>0.4953184984302266</v>
       </c>
       <c r="J19" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>8.25</v>
+        <v>0.4953184984302266</v>
       </c>
     </row>
     <row r="20">
@@ -1161,36 +1161,36 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>22.75</v>
+        <v>0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4.15</v>
       </c>
       <c r="E20" t="n">
-        <v>22.75</v>
+        <v>3.148711502134913</v>
       </c>
       <c r="F20" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>8.25</v>
+        <v>3.148711502134913</v>
       </c>
       <c r="H20" t="n">
-        <v>22.75</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>22.75</v>
+        <v>0.5669602883288144</v>
       </c>
       <c r="J20" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>8.25</v>
+        <v>0.5669602883288144</v>
       </c>
     </row>
     <row r="21">
@@ -1198,35 +1198,960 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.148711502134913</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.148711502134913</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6233184618414203</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.6233184618414203</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DLVL_NaS_s_300 MWh</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>300</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.003488360334833763</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.003488360334833763</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>47849</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DLVL_NaS_s_300 MWh</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>300</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.005504795012061275</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.005504795012061275</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>49675</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DLVL_NaS_s_300 MWh</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>300</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.006851905894951468</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.006851905894951468</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>51502</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DLVL_NaS_s_300 MWh</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>300</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.007842950655215265</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.007842950655215265</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>53328</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DLVL_NaS_s_300 MWh</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>300</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.04355717577953296</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.008622572055472981</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.008622572055472981</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DLVL_VRF_s_500 kWh</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.093016200900258</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.093016200900258</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>47849</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DLVL_VRF_s_500 kWh</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.302877007236764</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.302877007236764</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>49675</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DLVL_VRF_s_500 kWh</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.11114353697088</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.11114353697088</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>51502</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DLVL_VRF_s_500 kWh</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.705770393129159</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.705770393129159</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>53328</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DLVL_VRF_s_500 kWh</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>26.13430546771977</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5.173543233283787</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.173543233283787</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>100</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>47849</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>49675</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>100</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>51502</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>53328</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>100</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>47849</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>100</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>49675</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>100</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>100</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>51502</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>100</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>100</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>53328</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1.07269491826949</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>RE_GPV_s_1 MW</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
         <v>22.75</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="F42" t="n">
+        <v>1.072694969729275</v>
+      </c>
+      <c r="G42" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.072588669647553</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.072537104954585</v>
+      </c>
+      <c r="K42" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>47849</v>
+      </c>
+      <c r="B43" t="n">
+        <v>17.59976059515704</v>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D43" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E43" t="n">
         <v>22.75</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F43" t="n">
+        <v>17.59976092988197</v>
+      </c>
+      <c r="G43" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="H43" t="n">
         <v>8.25</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I43" t="n">
         <v>8.25</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J43" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="K43" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>49675</v>
+      </c>
+      <c r="B44" t="n">
         <v>22.75</v>
       </c>
-      <c r="I21" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>RE_GPV_s_1 MW</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
         <v>22.75</v>
       </c>
-      <c r="J21" t="n">
+      <c r="F44" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G44" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="H44" t="n">
         <v>8.25</v>
       </c>
-      <c r="K21" t="n">
+      <c r="I44" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J44" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>51502</v>
+      </c>
+      <c r="B45" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>RE_GPV_s_1 MW</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G45" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="H45" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="K45" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>53328</v>
+      </c>
+      <c r="B46" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>RE_GPV_s_1 MW</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G46" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J46" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="K46" t="n">
         <v>8.25</v>
       </c>
     </row>
